--- a/DRAGO/Diciembre/EXPENSAS-Diciembre.xlsx
+++ b/DRAGO/Diciembre/EXPENSAS-Diciembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217915E1-8EA5-4251-8260-0DF3FDBE6CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4B0A38-BFB2-49D9-95BE-F08A514D3583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$32</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
@@ -274,9 +274,6 @@
     <t>LAS EXPENSAS SE TRANSFIEREN A UNA CUENTA DE MERCADO PAGO: ALIAS: carolina.canciani CVU: 0000003100080478547818</t>
   </si>
   <si>
-    <t>Colocacion de membarana en techo - A dos aguas - Material y mano de obra</t>
-  </si>
-  <si>
     <t>SALDO</t>
   </si>
   <si>
@@ -298,13 +295,16 @@
     <t>Nicolas - Fumigacion 16/12</t>
   </si>
   <si>
-    <t>Cerrajeria Citta</t>
-  </si>
-  <si>
-    <t>Servisur</t>
-  </si>
-  <si>
     <t>Casa Ruan - Compra de materiales electricos</t>
+  </si>
+  <si>
+    <t>Servisur - Cambio de fotocelulas - Reflectores</t>
+  </si>
+  <si>
+    <t>Cerrajeria Citta - Copia de llaves</t>
+  </si>
+  <si>
+    <t>Agustina</t>
   </si>
 </sst>
 </file>
@@ -844,7 +844,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1007,7 +1007,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1065,10 +1064,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1474,10 +1473,10 @@
         <v>35</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1530,7 +1529,7 @@
       <c r="B17" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="126">
+      <c r="C17" s="51">
         <v>43870.01</v>
       </c>
       <c r="D17" s="5"/>
@@ -1554,7 +1553,7 @@
       <c r="B19" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="126">
+      <c r="C19" s="51">
         <v>19878.330000000002</v>
       </c>
       <c r="D19" s="5"/>
@@ -1567,7 +1566,7 @@
         <v>31</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="127">
+      <c r="C20" s="125">
         <v>165203.49</v>
       </c>
       <c r="D20" s="38"/>
@@ -1610,7 +1609,7 @@
         <v>63</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="51">
         <f>68460+68460*5%</f>
@@ -1620,51 +1619,49 @@
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B25" s="59"/>
-      <c r="C25" s="126">
+      <c r="C25" s="51">
         <v>50000</v>
       </c>
       <c r="F25" s="18"/>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="59"/>
-      <c r="C26" s="51">
-        <v>32850</v>
-      </c>
+      <c r="C26" s="51"/>
       <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B27" s="59"/>
-      <c r="C27" s="126">
+      <c r="C27" s="51">
         <v>57000</v>
       </c>
       <c r="F27" s="18"/>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="59"/>
-      <c r="C28" s="126">
+      <c r="C28" s="51">
         <v>60000</v>
       </c>
       <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="104" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B29" s="59"/>
-      <c r="C29" s="126">
-        <v>394000</v>
+      <c r="C29" s="51">
+        <v>39400</v>
       </c>
       <c r="F29" s="18"/>
     </row>
@@ -1683,7 +1680,7 @@
       <c r="B31" s="58"/>
       <c r="C31" s="42">
         <f>SUM(C23:C30)</f>
-        <v>665733</v>
+        <v>278283</v>
       </c>
       <c r="F31" s="18"/>
     </row>
@@ -1694,7 +1691,7 @@
       <c r="B32" s="49"/>
       <c r="C32" s="60">
         <f>+C31+C22</f>
-        <v>952669.58</v>
+        <v>565219.57999999996</v>
       </c>
       <c r="F32" s="18"/>
     </row>
@@ -1710,19 +1707,15 @@
       <c r="F34" s="18"/>
     </row>
     <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="107"/>
-      <c r="B35" s="108"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="107"/>
       <c r="C35" s="100"/>
       <c r="F35" s="18"/>
     </row>
     <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="104" t="s">
-        <v>82</v>
-      </c>
+      <c r="A36" s="104"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="51">
-        <v>180000</v>
-      </c>
+      <c r="C36" s="51"/>
       <c r="F36" s="18"/>
     </row>
     <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -1742,7 +1735,7 @@
       <c r="B39" s="19"/>
       <c r="C39" s="20">
         <f>SUM(C35:C38)</f>
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="E39" s="12"/>
     </row>
@@ -1753,7 +1746,7 @@
       <c r="B41" s="29"/>
       <c r="C41" s="30">
         <f>+C39+C32</f>
-        <v>1132669.58</v>
+        <v>565219.57999999996</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1767,7 +1760,7 @@
       </c>
       <c r="B44" s="28"/>
       <c r="C44" s="33">
-        <v>66868.53562338918</v>
+        <v>-191015.42432661087</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -1778,18 +1771,18 @@
       </c>
       <c r="C45" s="27">
         <f>'prorrateo '!F13</f>
-        <v>425923.61005000002</v>
+        <v>467070.81255000003</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C46" s="105">
         <f>extraordinarias!E13</f>
-        <v>26352</v>
+        <v>14127.48</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
@@ -1800,7 +1793,7 @@
       </c>
       <c r="C47" s="61">
         <f>-C39</f>
-        <v>-180000</v>
+        <v>0</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
@@ -1811,7 +1804,7 @@
       </c>
       <c r="C48" s="61">
         <f>-(C32-C30)</f>
-        <v>-952669.58</v>
+        <v>-565219.57999999996</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1821,7 +1814,7 @@
       <c r="B49" s="28"/>
       <c r="C49" s="33">
         <f>SUM(C44:C48)</f>
-        <v>-613525.43432661076</v>
+        <v>-275036.71177661081</v>
       </c>
       <c r="D49" s="6"/>
     </row>
@@ -1927,7 +1920,7 @@
         <v>47</v>
       </c>
       <c r="E1" s="102">
-        <v>530159.57000000007</v>
+        <v>565219.57999999996</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
@@ -1955,58 +1948,58 @@
       <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="116" t="s">
+      <c r="A3" s="118"/>
+      <c r="B3" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="113" t="s">
+      <c r="C3" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="114" t="s">
+      <c r="D3" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="116" t="s">
+      <c r="E3" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="111" t="s">
+      <c r="F3" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="113" t="s">
+      <c r="G3" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="111" t="s">
+      <c r="H3" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="113" t="s">
+      <c r="I3" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="115" t="s">
+      <c r="J3" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="109" t="s">
+      <c r="K3" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="109" t="s">
+      <c r="L3" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="109" t="s">
+      <c r="M3" s="108" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="120"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="68">
@@ -2022,14 +2015,15 @@
         <v>58</v>
       </c>
       <c r="E5" s="37">
-        <v>52345.718659999991</v>
+        <v>64145.02663</v>
       </c>
       <c r="F5" s="85">
-        <v>52350</v>
+        <f>E5</f>
+        <v>64145.02663</v>
       </c>
       <c r="G5" s="37">
         <f>E5-F5</f>
-        <v>-4.2813400000086403</v>
+        <v>0</v>
       </c>
       <c r="H5" s="37">
         <f>IF(G5&gt;0,G5*3%,0)</f>
@@ -2041,15 +2035,15 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>64149.307970000009</v>
+        <v>68391.569179999991</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>64145.02663</v>
+        <v>68391.569179999991</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>66710.827695200001</v>
+        <v>71127.231947199994</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -2066,18 +2060,17 @@
         <v>59</v>
       </c>
       <c r="E6" s="37">
-        <v>52780.719699999994</v>
+        <v>64679.467540000005</v>
       </c>
       <c r="F6" s="85">
-        <f t="shared" ref="F6:F11" si="0">E6</f>
-        <v>52780.719699999994</v>
+        <v>67266.649999999994</v>
       </c>
       <c r="G6" s="37">
-        <f t="shared" ref="G6:G12" si="1">E6-F6</f>
-        <v>0</v>
+        <f t="shared" ref="G6:G12" si="0">E6-F6</f>
+        <v>-2587.1824599999891</v>
       </c>
       <c r="H6" s="37">
-        <f t="shared" ref="H6:H12" si="2">IF(G6&gt;0,G6*3%,0)</f>
+        <f t="shared" ref="H6:H12" si="1">IF(G6&gt;0,G6*3%,0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="74">
@@ -2086,15 +2079,15 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>64679.467540000005</v>
+        <v>68956.788759999996</v>
       </c>
       <c r="L6" s="75">
-        <f t="shared" ref="L6:L12" si="3">E6-F6+H6+K6+J6</f>
-        <v>64679.467540000005</v>
+        <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
+        <v>66369.606300000014</v>
       </c>
       <c r="M6" s="76">
-        <f t="shared" ref="M6:M12" si="4">L6+L6*4%</f>
-        <v>67266.646241599999</v>
+        <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
+        <v>69024.390552000012</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
@@ -2113,17 +2106,18 @@
         <v>72</v>
       </c>
       <c r="E7" s="37">
-        <v>50617.575449999997</v>
+        <v>18118.245140000006</v>
       </c>
       <c r="F7" s="85">
-        <v>94528</v>
+        <f>E7</f>
+        <v>18118.245140000006</v>
       </c>
       <c r="G7" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="37">
         <f t="shared" si="1"/>
-        <v>-43910.424550000003</v>
-      </c>
-      <c r="H7" s="37">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="74">
@@ -2132,15 +2126,15 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>62028.66969000001</v>
+        <v>66130.690860000002</v>
       </c>
       <c r="L7" s="75">
+        <f t="shared" si="2"/>
+        <v>66130.690860000002</v>
+      </c>
+      <c r="M7" s="76">
         <f t="shared" si="3"/>
-        <v>18118.245140000006</v>
-      </c>
-      <c r="M7" s="76">
-        <f t="shared" si="4"/>
-        <v>18842.974945600006</v>
+        <v>68775.918494400001</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2157,16 +2151,19 @@
         <v>74</v>
       </c>
       <c r="E8" s="85">
-        <v>50617.575449999997</v>
-      </c>
-      <c r="F8" s="106"/>
+        <v>118731</v>
+      </c>
+      <c r="F8" s="126">
+        <f>118731.36</f>
+        <v>118731.36</v>
+      </c>
       <c r="G8" s="37">
+        <f t="shared" si="0"/>
+        <v>-0.36000000000058208</v>
+      </c>
+      <c r="H8" s="37">
         <f t="shared" si="1"/>
-        <v>50617.575449999997</v>
-      </c>
-      <c r="H8" s="37">
-        <f t="shared" si="2"/>
-        <v>1518.5272634999999</v>
+        <v>0</v>
       </c>
       <c r="I8" s="74">
         <v>0.11700000000000001</v>
@@ -2174,15 +2171,18 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>62028.66969000001</v>
+        <v>66130.690860000002</v>
       </c>
       <c r="L8" s="75">
+        <f t="shared" si="2"/>
+        <v>66130.330860000002</v>
+      </c>
+      <c r="M8" s="76">
         <f t="shared" si="3"/>
-        <v>114164.77240350001</v>
-      </c>
-      <c r="M8" s="76">
-        <f t="shared" si="4"/>
-        <v>118731.36329964001</v>
+        <v>68775.5440944</v>
+      </c>
+      <c r="N8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -2199,19 +2199,18 @@
         <v>57</v>
       </c>
       <c r="E9" s="37">
-        <v>59270.152450000001</v>
+        <v>72631.86109000002</v>
       </c>
       <c r="F9" s="85">
-        <f>E9</f>
-        <v>59270.152450000001</v>
+        <v>64149</v>
       </c>
       <c r="G9" s="37">
+        <f t="shared" si="0"/>
+        <v>8482.8610900000203</v>
+      </c>
+      <c r="H9" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>254.4858327000006</v>
       </c>
       <c r="I9" s="74">
         <v>0.13700000000000001</v>
@@ -2219,15 +2218,15 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>72631.86109000002</v>
+        <v>77435.082460000005</v>
       </c>
       <c r="L9" s="75">
+        <f t="shared" si="2"/>
+        <v>86172.429382700022</v>
+      </c>
+      <c r="M9" s="76">
         <f t="shared" si="3"/>
-        <v>72631.86109000002</v>
-      </c>
-      <c r="M9" s="76">
-        <f t="shared" si="4"/>
-        <v>75537.135533600027</v>
+        <v>89619.326558008019</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -2244,18 +2243,16 @@
         <v>77</v>
       </c>
       <c r="E10" s="37">
-        <v>129184.55865799999</v>
-      </c>
-      <c r="F10" s="85">
-        <v>57107.01</v>
-      </c>
+        <v>144220.93835774</v>
+      </c>
+      <c r="F10" s="85"/>
       <c r="G10" s="37">
+        <f t="shared" si="0"/>
+        <v>144220.93835774</v>
+      </c>
+      <c r="H10" s="37">
         <f t="shared" si="1"/>
-        <v>72077.548657999985</v>
-      </c>
-      <c r="H10" s="37">
-        <f t="shared" si="2"/>
-        <v>2162.3264597399993</v>
+        <v>4326.6281507322001</v>
       </c>
       <c r="I10" s="74">
         <v>0.13200000000000001</v>
@@ -2263,15 +2260,15 @@
       <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>69981.063240000018</v>
+        <v>74608.984559999997</v>
       </c>
       <c r="L10" s="75">
+        <f t="shared" si="2"/>
+        <v>223156.55106847221</v>
+      </c>
+      <c r="M10" s="76">
         <f t="shared" si="3"/>
-        <v>144220.93835774</v>
-      </c>
-      <c r="M10" s="76">
-        <f t="shared" si="4"/>
-        <v>149989.7758920496</v>
+        <v>232082.81311121109</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -2288,18 +2285,18 @@
         <v>56</v>
       </c>
       <c r="E11" s="37">
-        <v>54943.863949999999</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="F11" s="85">
+        <f t="shared" ref="F11" si="4">E11</f>
+        <v>67330.265390000015</v>
+      </c>
+      <c r="G11" s="37">
         <f t="shared" si="0"/>
-        <v>54943.863949999999</v>
-      </c>
-      <c r="G11" s="37">
+        <v>0</v>
+      </c>
+      <c r="H11" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="37">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I11" s="74">
@@ -2308,15 +2305,15 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>67330.265390000015</v>
+        <v>71782.886659999989</v>
       </c>
       <c r="L11" s="75">
+        <f t="shared" si="2"/>
+        <v>71782.886659999989</v>
+      </c>
+      <c r="M11" s="76">
         <f t="shared" si="3"/>
-        <v>67330.265390000015</v>
-      </c>
-      <c r="M11" s="76">
-        <f t="shared" si="4"/>
-        <v>70023.476005600009</v>
+        <v>74654.202126399992</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -2333,18 +2330,18 @@
         <v>55</v>
       </c>
       <c r="E12" s="37">
-        <v>54943.863949999999</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="F12" s="85">
         <f>E12</f>
-        <v>54943.863949999999</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="G12" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="37">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="74">
@@ -2353,15 +2350,15 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>67330.265390000015</v>
+        <v>71782.886659999989</v>
       </c>
       <c r="L12" s="75">
+        <f t="shared" si="2"/>
+        <v>71782.886659999989</v>
+      </c>
+      <c r="M12" s="76">
         <f t="shared" si="3"/>
-        <v>67330.265390000015</v>
-      </c>
-      <c r="M12" s="76">
-        <f t="shared" si="4"/>
-        <v>70023.476005600009</v>
+        <v>74654.202126399992</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2373,16 +2370,16 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>504704.02826799999</v>
+        <v>617187.06953773997</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
-        <v>425923.61005000002</v>
+        <v>467070.81255000003</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>3680.8537232399995</v>
+        <v>4581.1139834322003</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
@@ -2394,61 +2391,61 @@
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>530159.57000000007</v>
+        <v>565219.57999999996</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>612620.84194124001</v>
+        <v>719916.95097117219</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>637125.67561888974</v>
+        <v>748713.62901001901</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
     </row>
     <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
     </row>
     <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
       <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -2458,16 +2455,16 @@
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
@@ -2475,16 +2472,16 @@
     <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
@@ -2496,16 +2493,16 @@
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
@@ -2518,16 +2515,16 @@
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
@@ -2540,16 +2537,16 @@
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
@@ -2562,16 +2559,16 @@
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
@@ -2584,16 +2581,16 @@
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="117"/>
+      <c r="L24" s="117"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
@@ -2606,16 +2603,16 @@
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="118"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="118"/>
-      <c r="L25" s="118"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="117"/>
+      <c r="L25" s="117"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
@@ -2628,16 +2625,16 @@
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="118"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="118"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
@@ -2650,16 +2647,16 @@
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-      <c r="K27" s="118"/>
-      <c r="L27" s="118"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="117"/>
+      <c r="L27" s="117"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
@@ -2670,68 +2667,68 @@
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="118"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="117"/>
+      <c r="I29" s="117"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="117"/>
+      <c r="L29" s="117"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="39"/>
@@ -2781,10 +2778,10 @@
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="121">
-        <v>0</v>
-      </c>
-      <c r="E1" s="121"/>
+      <c r="D1" s="120">
+        <v>0</v>
+      </c>
+      <c r="E1" s="120"/>
       <c r="F1" s="103"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
@@ -2810,49 +2807,49 @@
       <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="122" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116" t="s">
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="114" t="s">
+      <c r="D3" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="113" t="s">
+      <c r="E3" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="116" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="114" t="s">
+      <c r="F3" s="115" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="113" t="s">
+      <c r="H3" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="125" t="s">
+      <c r="I3" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="124" t="s">
+      <c r="J3" s="123" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="123"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="124"/>
+      <c r="A4" s="122"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="123"/>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -2866,18 +2863,18 @@
         <v>26</v>
       </c>
       <c r="D5" s="75">
-        <v>118177.84</v>
+        <v>121723.1752</v>
       </c>
       <c r="E5" s="75">
         <v>0</v>
       </c>
       <c r="F5" s="75">
         <f>D5-E5</f>
-        <v>118177.84</v>
+        <v>121723.1752</v>
       </c>
       <c r="G5" s="90">
         <f>F5*3%</f>
-        <v>3545.3352</v>
+        <v>3651.695256</v>
       </c>
       <c r="H5" s="74">
         <v>0.121</v>
@@ -2888,7 +2885,7 @@
       </c>
       <c r="J5" s="97">
         <f>+G5+I5+F5</f>
-        <v>121723.1752</v>
+        <v>125374.870456</v>
       </c>
       <c r="L5" s="17"/>
     </row>
@@ -2903,18 +2900,18 @@
         <v>27</v>
       </c>
       <c r="D6" s="75">
-        <v>149494.16</v>
+        <v>153978.98480000001</v>
       </c>
       <c r="E6" s="75">
         <v>0</v>
       </c>
       <c r="F6" s="75">
         <f t="shared" ref="F6:F12" si="1">D6-E6</f>
-        <v>149494.16</v>
+        <v>153978.98480000001</v>
       </c>
       <c r="G6" s="90">
         <f t="shared" ref="G6:G12" si="2">F6*3%</f>
-        <v>4484.8248000000003</v>
+        <v>4619.3695440000001</v>
       </c>
       <c r="H6" s="74">
         <v>0.122</v>
@@ -2925,7 +2922,7 @@
       </c>
       <c r="J6" s="97">
         <f t="shared" ref="J6:J12" si="3">+G6+I6+F6</f>
-        <v>153978.98480000001</v>
+        <v>158598.35434399999</v>
       </c>
       <c r="L6" s="17"/>
     </row>
@@ -2940,11 +2937,11 @@
         <v>28</v>
       </c>
       <c r="D7" s="75">
-        <v>12636</v>
+        <v>0</v>
       </c>
       <c r="E7" s="75">
         <f>D7</f>
-        <v>12636</v>
+        <v>0</v>
       </c>
       <c r="F7" s="75">
         <f t="shared" si="1"/>
@@ -2978,18 +2975,18 @@
         <v>29</v>
       </c>
       <c r="D8" s="75">
-        <v>143366.72</v>
+        <v>147667.72159999999</v>
       </c>
       <c r="E8" s="75">
         <v>0</v>
       </c>
       <c r="F8" s="75">
         <f t="shared" si="1"/>
-        <v>143366.72</v>
+        <v>147667.72159999999</v>
       </c>
       <c r="G8" s="90">
         <f t="shared" si="2"/>
-        <v>4301.0015999999996</v>
+        <v>4430.0316479999992</v>
       </c>
       <c r="H8" s="74">
         <v>0.11700000000000001</v>
@@ -3000,7 +2997,7 @@
       </c>
       <c r="J8" s="97">
         <f t="shared" si="3"/>
-        <v>147667.72159999999</v>
+        <v>152097.75324799999</v>
       </c>
       <c r="L8" s="17"/>
     </row>
@@ -3015,18 +3012,18 @@
         <v>26</v>
       </c>
       <c r="D9" s="75">
-        <v>133806.24000000002</v>
+        <v>137820.42720000003</v>
       </c>
       <c r="E9" s="75">
         <v>0</v>
       </c>
       <c r="F9" s="75">
         <f t="shared" si="1"/>
-        <v>133806.24000000002</v>
+        <v>137820.42720000003</v>
       </c>
       <c r="G9" s="90">
         <f t="shared" si="2"/>
-        <v>4014.1872000000003</v>
+        <v>4134.6128160000007</v>
       </c>
       <c r="H9" s="74">
         <v>0.13700000000000001</v>
@@ -3037,7 +3034,7 @@
       </c>
       <c r="J9" s="97">
         <f t="shared" si="3"/>
-        <v>137820.42720000003</v>
+        <v>141955.04001600004</v>
       </c>
       <c r="L9" s="17"/>
     </row>
@@ -3052,18 +3049,18 @@
         <v>26</v>
       </c>
       <c r="D10" s="75">
-        <v>128921.28</v>
+        <v>132788.9184</v>
       </c>
       <c r="E10" s="75">
         <v>0</v>
       </c>
       <c r="F10" s="75">
         <f t="shared" si="1"/>
-        <v>128921.28</v>
+        <v>132788.9184</v>
       </c>
       <c r="G10" s="90">
         <f t="shared" si="2"/>
-        <v>3867.6383999999998</v>
+        <v>3983.6675519999999</v>
       </c>
       <c r="H10" s="74">
         <v>0.13200000000000001</v>
@@ -3074,7 +3071,7 @@
       </c>
       <c r="J10" s="97">
         <f t="shared" si="3"/>
-        <v>132788.9184</v>
+        <v>136772.58595199999</v>
       </c>
       <c r="L10" s="17"/>
     </row>
@@ -3089,11 +3086,11 @@
         <v>28</v>
       </c>
       <c r="D11" s="75">
-        <v>13716</v>
+        <v>0</v>
       </c>
       <c r="E11" s="75">
         <f>D11</f>
-        <v>13716</v>
+        <v>0</v>
       </c>
       <c r="F11" s="75">
         <f t="shared" si="1"/>
@@ -3127,18 +3124,19 @@
         <v>30</v>
       </c>
       <c r="D12" s="75">
-        <v>13716</v>
+        <v>14127.48</v>
       </c>
       <c r="E12" s="75">
-        <v>0</v>
+        <f>D12</f>
+        <v>14127.48</v>
       </c>
       <c r="F12" s="75">
         <f t="shared" si="1"/>
-        <v>13716</v>
+        <v>0</v>
       </c>
       <c r="G12" s="90">
         <f t="shared" si="2"/>
-        <v>411.47999999999996</v>
+        <v>0</v>
       </c>
       <c r="H12" s="74">
         <v>0.127</v>
@@ -3149,7 +3147,7 @@
       </c>
       <c r="J12" s="97">
         <f t="shared" si="3"/>
-        <v>14127.48</v>
+        <v>0</v>
       </c>
       <c r="L12" s="17"/>
     </row>
@@ -3161,16 +3159,16 @@
       <c r="C13" s="79"/>
       <c r="D13" s="80">
         <f>SUM(D5:D12)</f>
-        <v>713834.24</v>
+        <v>708106.70719999995</v>
       </c>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>26352</v>
+        <v>14127.48</v>
       </c>
       <c r="F13" s="80"/>
       <c r="G13" s="80">
         <f>SUM(G5:G12)</f>
-        <v>20624.467199999999</v>
+        <v>20819.376816</v>
       </c>
       <c r="H13" s="70">
         <f t="shared" ref="H13" si="4">SUM(H5:H12)</f>
@@ -3182,7 +3180,7 @@
       </c>
       <c r="J13" s="81">
         <f>SUM(J5:J12)</f>
-        <v>708106.70719999995</v>
+        <v>714798.60401599994</v>
       </c>
       <c r="L13" s="17"/>
     </row>

--- a/DRAGO/Diciembre/EXPENSAS-Diciembre.xlsx
+++ b/DRAGO/Diciembre/EXPENSAS-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4B0A38-BFB2-49D9-95BE-F08A514D3583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB4DDA8-2BA2-4BCB-B559-4792BAAC8489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinarias" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$32</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="94">
   <si>
     <t>UF</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>Agustina</t>
+  </si>
+  <si>
+    <t>Alterini Guido - Mantenimiento de Jardin</t>
   </si>
 </sst>
 </file>
@@ -1007,12 +1010,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1034,21 +1056,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1064,10 +1071,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1435,17 +1438,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:H60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1453,22 +1456,22 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>35</v>
       </c>
@@ -1479,17 +1482,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1505,24 +1508,24 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="84"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
         <v>49</v>
       </c>
@@ -1535,7 +1538,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
         <v>62</v>
       </c>
@@ -1546,7 +1549,7 @@
       <c r="D18" s="38"/>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
         <v>42</v>
       </c>
@@ -1561,19 +1564,19 @@
       <c r="F19" s="14"/>
       <c r="H19" s="86"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="46" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="125">
+      <c r="C20" s="106">
         <v>165203.49</v>
       </c>
       <c r="D20" s="38"/>
       <c r="F20" s="12"/>
       <c r="H20" s="86"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
         <v>32</v>
       </c>
@@ -1589,7 +1592,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="57"/>
       <c r="B22" s="58"/>
       <c r="C22" s="42">
@@ -1597,14 +1600,14 @@
         <v>286936.57999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="56"/>
       <c r="C23" s="84"/>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="46" t="s">
         <v>63</v>
       </c>
@@ -1617,7 +1620,7 @@
       </c>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
         <v>88</v>
       </c>
@@ -1627,260 +1630,270 @@
       </c>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="51">
+        <v>90000</v>
+      </c>
+      <c r="F26" s="18"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="51"/>
-      <c r="F26" s="18"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46" t="s">
+      <c r="B27" s="59"/>
+      <c r="C27" s="51"/>
+      <c r="F27" s="18"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
         <v>91</v>
-      </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="51">
-        <v>57000</v>
-      </c>
-      <c r="F27" s="18"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46" t="s">
-        <v>90</v>
       </c>
       <c r="B28" s="59"/>
       <c r="C28" s="51">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="104" t="s">
-        <v>89</v>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="46" t="s">
+        <v>90</v>
       </c>
       <c r="B29" s="59"/>
       <c r="C29" s="51">
+        <v>60000</v>
+      </c>
+      <c r="F29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="104" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="59"/>
+      <c r="C30" s="51">
         <v>39400</v>
       </c>
-      <c r="F29" s="18"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="46" t="s">
+      <c r="F30" s="18"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="56"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="18"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="42">
-        <f>SUM(C23:C30)</f>
-        <v>278283</v>
-      </c>
+      <c r="B31" s="56"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="12"/>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49" t="s">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="57"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="42">
+        <f>SUM(C23:C31)</f>
+        <v>368283</v>
+      </c>
+      <c r="F32" s="18"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="60">
-        <f>+C31+C22</f>
-        <v>565219.57999999996</v>
-      </c>
-      <c r="F32" s="18"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C33" s="43"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="60">
+        <f>+C32+C22</f>
+        <v>655219.57999999996</v>
+      </c>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>43</v>
-      </c>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="43"/>
       <c r="F34" s="18"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="106"/>
-      <c r="B35" s="107"/>
-      <c r="C35" s="100"/>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="43"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="104"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="51"/>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="108"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="100"/>
       <c r="F36" s="18"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="104"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="52"/>
+      <c r="C37" s="51"/>
       <c r="F37" s="18"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C38" s="44"/>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="52"/>
       <c r="F38" s="18"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C39" s="44"/>
+      <c r="F39" s="18"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20">
-        <f>SUM(C35:C38)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="12"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="29" t="s">
+      <c r="B40" s="19"/>
+      <c r="C40" s="20">
+        <f>SUM(C36:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30">
-        <f>+C39+C32</f>
-        <v>565219.57999999996</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="B42" s="29"/>
+      <c r="C42" s="30">
+        <f>+C40+C33</f>
+        <v>655219.57999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="31" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="33">
+      <c r="B45" s="28"/>
+      <c r="C45" s="33">
         <v>-191015.42432661087</v>
       </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C46" s="27">
         <f>'prorrateo '!F13</f>
         <v>467070.81255000003</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="105">
+      <c r="C47" s="105">
         <f>extraordinarias!E13</f>
         <v>14127.48</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" s="61">
-        <f>-C39</f>
-        <v>0</v>
-      </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="61">
+        <f>-C40</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="61">
-        <f>-(C32-C30)</f>
-        <v>-565219.57999999996</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="31" t="s">
+      <c r="C49" s="61">
+        <f>-(C33-C31)</f>
+        <v>-655219.57999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="33">
-        <f>SUM(C44:C48)</f>
-        <v>-275036.71177661081</v>
-      </c>
-      <c r="D49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="16"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="28"/>
+      <c r="C50" s="33">
+        <f>SUM(C45:C49)</f>
+        <v>-365036.71177661081</v>
+      </c>
+      <c r="D50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
       <c r="B51" s="14"/>
       <c r="C51" s="16"/>
-      <c r="F51" s="62"/>
-    </row>
-    <row r="52" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="15"/>
       <c r="B52" s="14"/>
       <c r="C52" s="16"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="45" t="s">
+      <c r="F52" s="62"/>
+    </row>
+    <row r="53" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="16"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="64"/>
-      <c r="C53" s="65">
+      <c r="B54" s="64"/>
+      <c r="C54" s="65">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="50"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="49" t="s">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="46"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="50"/>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="47"/>
-      <c r="C55" s="48">
-        <f>SUM(C53:C54)</f>
+      <c r="B56" s="47"/>
+      <c r="C56" s="48">
+        <f>SUM(C54:C55)</f>
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
     </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1898,36 +1911,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="17"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E1" s="102">
-        <v>565219.57999999996</v>
+        <v>655219.57999999996</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/01</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS DICIEMBRE 2025</v>
@@ -1947,61 +1960,61 @@
       <c r="L2" s="66"/>
       <c r="M2" s="67"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="118"/>
-      <c r="B3" s="115" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="113"/>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="113" t="s">
+      <c r="D3" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="115" t="s">
+      <c r="E3" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="110" t="s">
+      <c r="F3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="112" t="s">
+      <c r="G3" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="110" t="s">
+      <c r="H3" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="112" t="s">
+      <c r="I3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="114" t="s">
+      <c r="J3" s="121" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="108" t="s">
+      <c r="K3" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="108" t="s">
+      <c r="L3" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="108" t="s">
+      <c r="M3" s="115" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="119"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="109"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="114"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
         <v>1</v>
       </c>
@@ -2035,18 +2048,18 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>68391.569179999991</v>
+        <v>79281.569179999991</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>68391.569179999991</v>
+        <v>79281.569179999991</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>71127.231947199994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>82452.831947199986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="68">
         <v>2</v>
       </c>
@@ -2079,20 +2092,20 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>68956.788759999996</v>
+        <v>79936.788759999996</v>
       </c>
       <c r="L6" s="75">
         <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
-        <v>66369.606300000014</v>
+        <v>77349.606300000014</v>
       </c>
       <c r="M6" s="76">
         <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
-        <v>69024.390552000012</v>
+        <v>80443.590552000009</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="68">
         <v>3</v>
       </c>
@@ -2126,18 +2139,18 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>66130.690860000002</v>
+        <v>76660.690860000002</v>
       </c>
       <c r="L7" s="75">
         <f t="shared" si="2"/>
-        <v>66130.690860000002</v>
+        <v>76660.690860000002</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="3"/>
-        <v>68775.918494400001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>79727.118494399998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="68">
         <v>4</v>
       </c>
@@ -2153,7 +2166,7 @@
       <c r="E8" s="85">
         <v>118731</v>
       </c>
-      <c r="F8" s="126">
+      <c r="F8" s="107">
         <f>118731.36</f>
         <v>118731.36</v>
       </c>
@@ -2171,21 +2184,21 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>66130.690860000002</v>
+        <v>76660.690860000002</v>
       </c>
       <c r="L8" s="75">
         <f t="shared" si="2"/>
-        <v>66130.330860000002</v>
+        <v>76660.330860000002</v>
       </c>
       <c r="M8" s="76">
         <f t="shared" si="3"/>
-        <v>68775.5440944</v>
+        <v>79726.744094399997</v>
       </c>
       <c r="N8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="68">
         <v>5</v>
       </c>
@@ -2218,18 +2231,18 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>77435.082460000005</v>
+        <v>89765.082460000005</v>
       </c>
       <c r="L9" s="75">
         <f t="shared" si="2"/>
-        <v>86172.429382700022</v>
+        <v>98502.429382700022</v>
       </c>
       <c r="M9" s="76">
         <f t="shared" si="3"/>
-        <v>89619.326558008019</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>102442.52655800802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="68">
         <v>6</v>
       </c>
@@ -2260,18 +2273,18 @@
       <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>74608.984559999997</v>
+        <v>86488.984559999997</v>
       </c>
       <c r="L10" s="75">
         <f t="shared" si="2"/>
-        <v>223156.55106847221</v>
+        <v>235036.55106847221</v>
       </c>
       <c r="M10" s="76">
         <f t="shared" si="3"/>
-        <v>232082.81311121109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>244438.0131112111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="68">
         <v>7</v>
       </c>
@@ -2305,18 +2318,18 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>71782.886659999989</v>
+        <v>83212.886659999989</v>
       </c>
       <c r="L11" s="75">
         <f t="shared" si="2"/>
-        <v>71782.886659999989</v>
+        <v>83212.886659999989</v>
       </c>
       <c r="M11" s="76">
         <f t="shared" si="3"/>
-        <v>74654.202126399992</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>86541.402126399989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="68">
         <v>8</v>
       </c>
@@ -2350,18 +2363,18 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>71782.886659999989</v>
+        <v>83212.886659999989</v>
       </c>
       <c r="L12" s="75">
         <f t="shared" si="2"/>
-        <v>71782.886659999989</v>
+        <v>83212.886659999989</v>
       </c>
       <c r="M12" s="76">
         <f t="shared" si="3"/>
-        <v>74654.202126399992</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>86541.402126399989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -2391,355 +2404,350 @@
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>565219.57999999996</v>
+        <v>655219.57999999996</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>719916.95097117219</v>
+        <v>809916.95097117219</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>748713.62901001901</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C15" s="117" t="s">
+        <v>842313.62901001924</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C15" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="110"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="117"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="117"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="117"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>5</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="117"/>
-      <c r="L24" s="117"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="110"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>6</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="117"/>
-      <c r="K25" s="117"/>
-      <c r="L25" s="117"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="110"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="110"/>
+      <c r="L26" s="110"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="117"/>
-      <c r="K27" s="117"/>
-      <c r="L27" s="117"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="117"/>
-      <c r="K28" s="117"/>
-      <c r="L28" s="117"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="117"/>
-      <c r="K29" s="117"/>
-      <c r="L29" s="117"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="110"/>
+      <c r="L30" s="110"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="110"/>
+      <c r="L31" s="110"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="110"/>
+      <c r="K32" s="110"/>
+      <c r="L32" s="110"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2749,6 +2757,11 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2759,29 +2772,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="91" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="120">
-        <v>0</v>
-      </c>
-      <c r="E1" s="120"/>
+      <c r="D1" s="122">
+        <v>0</v>
+      </c>
+      <c r="E1" s="122"/>
       <c r="F1" s="103"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
@@ -2789,7 +2802,7 @@
       <c r="J1" s="94"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
         <v>79</v>
       </c>
@@ -2806,53 +2819,53 @@
       <c r="J2" s="96"/>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="115" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="115" t="s">
+      <c r="C3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="113" t="s">
+      <c r="D3" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="112" t="s">
+      <c r="E3" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="115" t="s">
+      <c r="F3" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="113" t="s">
+      <c r="G3" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="112" t="s">
+      <c r="H3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="124" t="s">
+      <c r="I3" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="123" t="s">
+      <c r="J3" s="125" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="122"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="123"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="125"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="98">
         <v>1</v>
       </c>
@@ -2889,7 +2902,7 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="98">
         <v>2</v>
       </c>
@@ -2926,7 +2939,7 @@
       </c>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="98">
         <v>3</v>
       </c>
@@ -2964,7 +2977,7 @@
       </c>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="98">
         <v>4</v>
       </c>
@@ -3001,7 +3014,7 @@
       </c>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="98">
         <v>5</v>
       </c>
@@ -3038,7 +3051,7 @@
       </c>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>6</v>
       </c>
@@ -3075,7 +3088,7 @@
       </c>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="98">
         <v>7</v>
       </c>
@@ -3113,7 +3126,7 @@
       </c>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>8</v>
       </c>
@@ -3151,7 +3164,7 @@
       </c>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
